--- a/plantillas/inventario-sistemas-ia.xlsx
+++ b/plantillas/inventario-sistemas-ia.xlsx
@@ -1001,7 +1001,7 @@
       </c>
       <c r="O7" s="8" t="inlineStr">
         <is>
-          <t>Coordinadora de contabilidad</t>
+          <t>Gerente del área contable</t>
         </is>
       </c>
       <c r="P7" s="8" t="inlineStr">
